--- a/株式会社慈久庵/【慈久庵】登記簿等取得確認リスト_261021.xlsx
+++ b/株式会社慈久庵/【慈久庵】登記簿等取得確認リスト_261021.xlsx
@@ -14,7 +14,7 @@
     <sheet name="03_未確定・追加確認" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">01_取得リスト!$A$4:$O$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">01_取得リスト!$A$4:$O$19</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="232">
   <si>
     <t xml:space="preserve">登記簿等 取得確認リスト｜株式会社慈久庵</t>
   </si>
@@ -298,6 +298,186 @@
   </si>
   <si>
     <t xml:space="preserve">⑥ 当社は株券発行会社である（法人登記簿）。株券の現物の有無・所在は登記簿では分からないため、別途ヒアリングで確認する。株式の譲渡には取締役会の承認を要する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⑦【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日 追記】受領した不動産関係書類により、管轄は水戸地方法務局 常陸太田支局、本店の所在は「天下野町字桜石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番」と確定した。あわせて、滑川里美氏（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2175</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）および長嶋新一氏（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2178-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2174-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）からの土地取得に関する書類（公図・登記原因証明情報・売買契約署名欄・手書きメモ）を確認。いずれも地目が畑・原野であり、農地法の制約と取得の完了状況が新たな論点となる。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">件数集計</t>
@@ -430,7 +610,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -555,7 +735,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">水戸地方法務局（管轄は要確認）</t>
+    <t xml:space="preserve">水戸地方法務局 常陸太田支局</t>
   </si>
   <si>
     <t xml:space="preserve">所在指定（土地）</t>
@@ -620,7 +800,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">法人登記簿（本店所在地）／</t>
+      <t xml:space="preserve">法人登記簿／</t>
     </r>
     <r>
       <rPr>
@@ -658,7 +838,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">千円</t>
+      <t xml:space="preserve">千円／公図（令和元年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日交付・所在「天下野町字桜石」地番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番）</t>
     </r>
   </si>
   <si>
@@ -891,119 +1128,1284 @@
     <t xml:space="preserve">RE-N01</t>
   </si>
   <si>
+    <t xml:space="preserve">滑川 里美 氏（取得交渉先）</t>
+  </si>
+  <si>
     <t xml:space="preserve">土地（農地）／全部事項証明書</t>
   </si>
   <si>
-    <t xml:space="preserve">名寄帳・ヒアリングで特定後に所在指定</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2175</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受領資料の手書きメモに「滑川里美氏所有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161-1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">畑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">407</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2161-2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">畑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">212</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162-1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">917</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2175 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">畑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">472</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡」の記載。別紙の登記原因証明情報では当社が滑川里美氏から取得している。取得済か交渉中かを登記簿で確定させる。地目が畑・原野のため農地法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条の制約を確認。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産関係書類（公図・登記原因証明情報・手書きメモ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE-N02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長嶋 新一 氏（取得交渉先）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2178</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2174</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同メモに「長嶋新一氏所有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2178-3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">512</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2174-1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">畑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">292</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡」の記載。別紙に長嶋新一氏（常陸太田市新宿町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">154</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番地）および相続人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の署名押印がある。取得済か否か、相続登記の完了状況を確認。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産関係書類（売買契約署名欄・手書きメモ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE-P01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小川 宣夫／小川 喜久子（個人）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個人名義の名寄帳で洗い出してから所在指定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代表者・配偶者が店舗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">階に居住。事業用資産が個人名義で混在していないかを確定させる。明渡し・賃貸借条件の整理にも必要。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">法人登記簿（代表取締役の住所）／面談ヒアリング</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商業登記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">履歴事項全部証明書</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天下野町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番地</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会社法人等番号 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0500-01-026647</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">法務局（オンライン請求可）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会社法人等番号で請求</t>
+  </si>
+  <si>
+    <t xml:space="preserve">－</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取得済。株式の譲渡制限は「取締役会の承認」。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">株券発行会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">である点に留意し、株券の現物の有無・所在を別途確認する（不発行なら定款変更の要否）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">概要／株式会社慈久庵法人登記簿（全部事項）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CO-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社慈久庵咸亨酒</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天下野町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162-1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">会社法人等番号 要確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商号・本店で請求</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出資金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円の出資先。事業内容・株主構成・役員・当社との取引関係、本件での取扱い（譲渡対象に含めるか）を確認。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期 勘定科目内訳明細書（出資金 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／常陸太田市天下野町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2162-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CO-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社慈久庵伊勢又</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中城町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">199-3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出資金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円の出資先。棚卸資産「伊勢又預け分」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">329</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円の預け先との同一性、在庫の実在性・所有権の確認につながる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期 勘定科目内訳明細書（出資金 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／常陸太田市中城町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">199-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CO-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代表者が役員を務める他の法人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヒアリングで法人名を特定後に請求</t>
   </si>
   <si>
     <t xml:space="preserve">中</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">焼き畑によるそば栽培地。所有か賃借かが未確定。所有であれば登記地目（田・畑）と農地法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条の制約、本件譲渡対象に含めるか否かを確認。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">面談ヒアリング／掲載誌</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE-P01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小川 宣夫／小川 喜久子（個人）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">個人名義の名寄帳で洗い出してから所在指定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">代表者・配偶者が店舗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">階に居住。事業用資産が個人名義で混在していないかを確定させる。明渡し・賃貸借条件の整理にも必要。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">法人登記簿（代表取締役の住所）／面談ヒアリング</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商業登記</t>
-  </si>
-  <si>
-    <t xml:space="preserve">履歴事項全部証明書</t>
+    <t xml:space="preserve">兼任の有無、関連当事者取引の有無を確認。未収入金の相手先「小びと」等の法人格もあわせて確認する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">面談ヒアリング／取引先シート（小びと 等 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">698,819</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">その他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社慈久庵／小川 宣夫／小川 喜久子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固定資産課税台帳（名寄帳）・固定資産評価証明書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常陸太田市 税務課</t>
+  </si>
+  <si>
+    <t xml:space="preserve">窓口・郵送（法人は代表者印、個人分は委任状が必要）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最優先</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本リストの起点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法人名義・個人名義それぞれの全不動産を地番単位で洗い出す。これを取らないと登記簿を請求する地番が確定せず、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RE-S01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RE-N01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RE-P01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は着手できない。評価額は時価純資産の算定にも使う。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">－（未受領。案件マスター「その他」Ⅱ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の未回収資料）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">OT-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公図・地積測量図・建物図面</t>
   </si>
   <si>
     <r>
@@ -1023,6 +2425,42 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">2162 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ほか</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">法務局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地番確定後に請求</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公図（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2162</t>
     </r>
     <r>
@@ -1032,702 +2470,37 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">番地</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">会社法人等番号 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0500-01-026647</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">法務局（オンライン請求可）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会社法人等番号で請求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">－</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">取得済。株式の譲渡制限は「取締役会の承認」。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">株券発行会社</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">である点に留意し、株券の現物の有無・所在を別途確認する（不発行なら定款変更の要否）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">概要／株式会社慈久庵法人登記簿（全部事項）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CO-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社慈久庵咸亨酒</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">天下野町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2162-1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">会社法人等番号 要確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商号・本店で請求</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出資金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千円の出資先。事業内容・株主構成・役員・当社との取引関係、本件での取扱い（譲渡対象に含めるか）を確認。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期 勘定科目内訳明細書（出資金 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,000,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円／常陸太田市天下野町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2162-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CO-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社慈久庵伊勢又</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中城町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">199-3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出資金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千円の出資先。棚卸資産「伊勢又預け分」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">329</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千円の預け先との同一性、在庫の実在性・所有権の確認につながる。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期 勘定科目内訳明細書（出資金 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円／常陸太田市中城町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">199-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CO-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">代表者が役員を務める他の法人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ヒアリングで法人名を特定後に請求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兼任の有無、関連当事者取引の有無を確認。未収入金の相手先「小びと」等の法人格もあわせて確認する。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">面談ヒアリング／取引先シート（小びと 等 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">698,819</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">その他</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社慈久庵／小川 宣夫／小川 喜久子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">固定資産課税台帳（名寄帳）・固定資産評価証明書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">常陸太田市 税務課</t>
-  </si>
-  <si>
-    <t xml:space="preserve">窓口・郵送（法人は代表者印、個人分は委任状が必要）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最優先</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本リストの起点。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">** </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法人名義・個人名義それぞれの全不動産を地番単位で洗い出す。これを取らないと登記簿を請求する地番が確定せず、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RE-S01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RE-N01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RE-P01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は着手できない。評価額は時価純資産の算定にも使う。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">－（未受領。案件マスター「その他」Ⅱ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の未回収資料）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">OT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公図・地積測量図・建物図面</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">天下野町</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2162 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ほか</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">法務局</t>
-  </si>
-  <si>
-    <t xml:space="preserve">地番確定後に請求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">境界・接道・越境の有無、駐車場の範囲、店舗建物の位置関係。面積の裏付けがないまま時価評価を行っている状態の解消。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案件マスター「不動産</t>
+      <t xml:space="preserve">番・字桜石・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は受領済。地積測量図と建物図面が未入手であり、各筆の地積・境界・接道、駐車場の範囲、店舗建物の位置関係を確定させる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公図（受領済）／案件マスター「不動産</t>
     </r>
     <r>
       <rPr>
@@ -4055,7 +4828,7 @@
     <tabColor rgb="FF17365D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -4160,194 +4933,188 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$18,"RE-*")</f>
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"RE-*",01_取得リスト!$A$5:$A$18,"取得済")</f>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$19,"RE-*")</f>
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"RE-*",01_取得リスト!$A$5:$A$19,"取得済")</f>
         <v>0</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"RE-*",01_取得リスト!$A$5:$A$18,"未取得")</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"RE-*",01_取得リスト!$M$5:$M$18,"高")+COUNTIFS(01_取得リスト!$C$5:$C$18,"RE-*",01_取得リスト!$M$5:$M$18,"最優先")</f>
-        <v>5</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$18,"CO-*")</f>
+      <c r="D15" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"RE-*",01_取得リスト!$A$5:$A$19,"未取得")</f>
+        <v>7</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"RE-*",01_取得リスト!$M$5:$M$19,"高")+COUNTIFS(01_取得リスト!$C$5:$C$19,"RE-*",01_取得リスト!$M$5:$M$19,"最優先")</f>
+        <v>7</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$19,"CO-*")</f>
         <v>4</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"CO-*",01_取得リスト!$A$5:$A$18,"取得済")</f>
+      <c r="C16" s="8" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"CO-*",01_取得リスト!$A$5:$A$19,"取得済")</f>
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"CO-*",01_取得リスト!$A$5:$A$18,"未取得")</f>
+      <c r="D16" s="8" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"CO-*",01_取得リスト!$A$5:$A$19,"未取得")</f>
         <v>3</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"CO-*",01_取得リスト!$M$5:$M$18,"高")+COUNTIFS(01_取得リスト!$C$5:$C$18,"CO-*",01_取得リスト!$M$5:$M$18,"最優先")</f>
+      <c r="E16" s="8" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"CO-*",01_取得リスト!$M$5:$M$19,"高")+COUNTIFS(01_取得リスト!$C$5:$C$19,"CO-*",01_取得リスト!$M$5:$M$19,"最優先")</f>
         <v>2</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$18,"OT-*")</f>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <f aca="false">COUNTIF(01_取得リスト!$C$5:$C$19,"OT-*")</f>
         <v>4</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"OT-*",01_取得リスト!$A$5:$A$18,"取得済")</f>
+      <c r="C17" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"OT-*",01_取得リスト!$A$5:$A$19,"取得済")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"OT-*",01_取得リスト!$A$5:$A$18,"未取得")</f>
+      <c r="D17" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"OT-*",01_取得リスト!$A$5:$A$19,"未取得")</f>
         <v>4</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$18,"OT-*",01_取得リスト!$M$5:$M$18,"高")+COUNTIFS(01_取得リスト!$C$5:$C$18,"OT-*",01_取得リスト!$M$5:$M$18,"最優先")</f>
+      <c r="E17" s="7" t="n">
+        <f aca="false">COUNTIFS(01_取得リスト!$C$5:$C$19,"OT-*",01_取得リスト!$M$5:$M$19,"高")+COUNTIFS(01_取得リスト!$C$5:$C$19,"OT-*",01_取得リスト!$M$5:$M$19,"最優先")</f>
         <v>2</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <f aca="false">SUM(B14:B16)</f>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <f aca="false">SUM(B15:B17)</f>
+        <v>15</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <f aca="false">SUM(C15:C17)</f>
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">SUM(D15:D17)</f>
         <v>14</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <f aca="false">SUM(C14:C16)</f>
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">SUM(D14:D16)</f>
-        <v>13</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">SUM(E14:E16)</f>
-        <v>9</v>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="E18" s="9" t="n">
+        <f aca="false">SUM(E15:E17)</f>
+        <v>11</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="D21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
@@ -4356,34 +5123,53 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
     </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4401,7 +5187,7 @@
     <tabColor rgb="FF0F6B78"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -4422,593 +5208,593 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="K8" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>92</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B11" s="16"/>
       <c r="C11" s="17" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="M11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="O11" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="16"/>
+      <c r="B12" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="C12" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L12" s="8" t="s">
+      <c r="N12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="M12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" s="8" t="s">
+      <c r="O12" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="O12" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="H14" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="O14" s="8" t="s">
         <v>119</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="17" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="K15" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="M15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="N15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="O15" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="F16" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>129</v>
       </c>
       <c r="I16" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="M16" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="M16" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="N16" s="8" t="s">
+      <c r="N16" s="18" t="s">
         <v>133</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -5017,32 +5803,32 @@
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="17" t="s">
         <v>135</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>136</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>138</v>
@@ -5051,7 +5837,7 @@
         <v>139</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>140</v>
@@ -5062,51 +5848,96 @@
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="18" t="s">
         <v>142</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>143</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>100</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O18"/>
+  <autoFilter ref="A4:O19"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5136,216 +5967,216 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>173</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -5378,32 +6209,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5411,19 +6242,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5431,19 +6262,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5451,19 +6282,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5471,19 +6302,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5491,19 +6322,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5511,19 +6342,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5531,19 +6362,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5551,19 +6382,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5571,19 +6402,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5591,19 +6422,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
